--- a/data/rob2_domain_scores.xlsx
+++ b/data/rob2_domain_scores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jayceekennett/Documents/GitHub/LSR6_CBM_H/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4B6E16-AB6D-6147-AE04-6C486DB158DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB551423-9C52-5341-B9B9-AE39B6B70208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16040" xr2:uid="{4FB782D7-0300-4984-901D-7AB4F5391D80}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="16040" activeTab="1" xr2:uid="{4FB782D7-0300-4984-901D-7AB4F5391D80}"/>
   </bookViews>
   <sheets>
     <sheet name="SAD_N" sheetId="18" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="77">
   <si>
     <t>Study*</t>
   </si>
@@ -456,7 +456,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="26">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -655,17 +662,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7CDE1174-4BC8-4136-A129-D4BCB2CF9059}" name="Table2" displayName="Table2" ref="A1:H41" totalsRowShown="0" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7CDE1174-4BC8-4136-A129-D4BCB2CF9059}" name="Table2" displayName="Table2" ref="A1:H41" totalsRowShown="0" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
   <autoFilter ref="A1:H41" xr:uid="{7CDE1174-4BC8-4136-A129-D4BCB2CF9059}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{A51A4F78-EFB5-4BA1-B287-EEF13EECBC91}" name="Study*" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{EA69040A-3E5F-4944-A184-357A0A9B26AC}" name="Outcome" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{7375EB92-5D2C-457B-9553-453E64E79F2D}" name="1" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{207D8DC2-720B-475E-A975-32CD6217B323}" name="2" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{47CB2AE8-7B28-40C4-8BDE-C724B29668EF}" name="3" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{720A158E-9208-4175-A5C1-07E34B213795}" name="4" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{4133C0FA-99D1-4236-9E36-FFB3D3BB9A2E}" name="5" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{BFFF3F6B-203E-4DE4-AB43-7ED2573BAB7E}" name="overall" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{A51A4F78-EFB5-4BA1-B287-EEF13EECBC91}" name="Study*" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{EA69040A-3E5F-4944-A184-357A0A9B26AC}" name="Outcome" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{7375EB92-5D2C-457B-9553-453E64E79F2D}" name="1" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{207D8DC2-720B-475E-A975-32CD6217B323}" name="2" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{47CB2AE8-7B28-40C4-8BDE-C724B29668EF}" name="3" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{720A158E-9208-4175-A5C1-07E34B213795}" name="4" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{4133C0FA-99D1-4236-9E36-FFB3D3BB9A2E}" name="5" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{BFFF3F6B-203E-4DE4-AB43-7ED2573BAB7E}" name="overall" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1051,7 +1058,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:G3">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FALSE">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2156,7 +2163,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7755FB0C-7480-1846-8330-2A5CD5300BFA}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -2263,15 +2270,46 @@
         <v>60</v>
       </c>
     </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C2:G4">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="FALSE">
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="FALSE">
+    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",I2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5:G5">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FALSE">
+      <formula>NOT(ISERROR(SEARCH("FALSE",C5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5781,6 +5819,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C9667EA7A926CE44956D0B5DCD9CC853" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2974ddbe2e2d0d4e5eed71132d632e4f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d306db0-a384-4295-b85c-939a3142a74b" xmlns:ns3="a3c2bd72-a5a7-4afd-b193-b6de680f91cc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c3a802fcff40337e478bae9a8b0bfda6" ns2:_="" ns3:_="">
     <xsd:import namespace="1d306db0-a384-4295-b85c-939a3142a74b"/>
@@ -5981,15 +6028,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -5997,6 +6035,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5E43BDA-E9E7-47B8-A41E-7C46F3C1C143}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A83A1DE-CF35-436F-82CA-1F7C23FF760F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6011,14 +6057,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5E43BDA-E9E7-47B8-A41E-7C46F3C1C143}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
